--- a/diseases/d133/2015-2019.xlsx
+++ b/diseases/d133/2015-2019.xlsx
@@ -18068,6 +18068,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18216,6 +18221,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19150,6 +19160,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19691,6 +19706,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19839,6 +19859,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20380,6 +20405,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20526,6 +20556,11 @@
       <c r="S104" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
